--- a/reports/HMC-Sanaad-Backend-Tasks.xlsx
+++ b/reports/HMC-Sanaad-Backend-Tasks.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -37,15 +37,36 @@
     <t>Deploy</t>
   </si>
   <si>
-    <t>Redeploy staging with latest main</t>
-  </si>
-  <si>
-    <t>Latest main carries: person_id support on GET /leave/lov/amend (view is person-scoped per DB team), composite-format Swagger examples for leave amend/cancel/return, PERSON_ID rules, corrected DTO docs. Staging Swagger must match the verified Postman collection.</t>
+    <t>Redeploy staging with latest main (contains the ORA-00027 workaround)</t>
+  </si>
+  <si>
+    <t>The backend now clears DBMS_SESSION identifier + DBMS_APPLICATION_INFO action/module before every PL/SQL call, which neutralises the EBS "kill the user's SSHR sessions" loop that was killing our own pooled session (ORA-00027 on school-fees/leave-apply/dependents-update). Also carries person_id support on GET /leave/lov/amend, the composite leave formats, the school-fees composite child name and the dependents-delete code rule. Re-verify those three endpoints right after the deploy.</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
+    <t>Verify</t>
+  </si>
+  <si>
+    <t>After the deploy: re-run dependents/update, leave/apply and school-fees several times</t>
+  </si>
+  <si>
+    <t>They shared the ORA-00027 defect; with the session-label fix they should stop failing intermittently. Use tools/resilient-runner.js with the phase cases, then regenerate the collection + reports.</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>School-fees submit exceeds the 30 s HTTP timeout while succeeding in Oracle</t>
+  </si>
+  <si>
+    <t>Verified: the client received 504 but the procedure committed with p_success_flag=Y. Either raise REQUEST_TIMEOUT_MS for submit routes, or return 202 + a way to confirm; mobile must not treat 504 as failure (duplicate submissions).</t>
+  </si>
+  <si>
     <t>Environment</t>
   </si>
   <si>
@@ -77,9 +98,6 @@
   </si>
   <si>
     <t>Blockers file: reports/HMC-Sanaad-DB-Team-Report.xlsx. Re-run the Postman collection / tools scripts to refresh captured examples after fixes.</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
   </si>
   <si>
     <t>Return objectVersionNumber with profile phones[]</t>
@@ -623,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -691,15 +709,15 @@
         <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>15</v>
@@ -711,7 +729,7 @@
         <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -722,27 +740,27 @@
         <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>23</v>
@@ -758,8 +776,8 @@
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>22</v>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>26</v>
@@ -771,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -779,19 +797,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -799,19 +817,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -819,19 +837,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -839,59 +857,59 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>43</v>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -899,18 +917,58 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>10</v>
       </c>
     </row>

--- a/reports/HMC-Sanaad-Backend-Tasks.xlsx
+++ b/reports/HMC-Sanaad-Backend-Tasks.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -49,15 +49,24 @@
     <t>Verify</t>
   </si>
   <si>
-    <t>After the deploy: re-run dependents/update, leave/apply and school-fees several times</t>
-  </si>
-  <si>
-    <t>They shared the ORA-00027 defect; with the session-label fix they should stop failing intermittently. Use tools/resilient-runner.js with the phase cases, then regenerate the collection + reports.</t>
+    <t>After the deploy: re-run dependents/update, leave/apply, school-fees AND letters/apply</t>
+  </si>
+  <si>
+    <t>The first three shared the ORA-00027 defect (session-label fix); letters/apply carries the new rules (valid name+language pair, no p_country). Use tools/resilient-runner.js with the phase cases, then regenerate the collection + reports.</t>
   </si>
   <si>
     <t>MEDIUM</t>
   </si>
   <si>
+    <t>Tooling</t>
+  </si>
+  <si>
+    <t>Dev console now sends SQL base64-encoded (WAF workaround)</t>
+  </si>
+  <si>
+    <t>The F5/WAF in front of staging rejects any request body that looks like SQL, which silently broke the worksheet (HTML "Request Rejected" instead of JSON). /execute and /explain accept `sqlB64`; the page uses it automatically. Same trick is available to any internal tooling that must post SQL.</t>
+  </si>
+  <si>
     <t>Timeout</t>
   </si>
   <si>
@@ -182,9 +191,6 @@
   </si>
   <si>
     <t>Proxied business routes are invisible in the public swagger; consider serving the backend swagger (or a filtered copy) through the gateway for partners.</t>
-  </si>
-  <si>
-    <t>Tooling</t>
   </si>
   <si>
     <t>Keep tools/ scripts as the regeneration source</t>
@@ -641,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -736,8 +742,8 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
+      <c r="B5" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>18</v>
@@ -749,7 +755,7 @@
         <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -760,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -780,36 +786,36 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>14</v>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -820,16 +826,16 @@
         <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -840,16 +846,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,7 +875,7 @@
         <v>41</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -880,16 +886,16 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -900,7 +906,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>47</v>
@@ -909,27 +915,27 @@
         <v>48</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>49</v>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -937,19 +943,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -957,7 +963,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>57</v>
@@ -969,6 +975,26 @@
         <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>10</v>
       </c>
     </row>
